--- a/results/link-prediction-gcn/Link/3shot/CiteSeer/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/CiteSeer/GCN_total_results.xlsx
@@ -903,12 +903,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.4582±0.0000</t>
+          <t>0.4766±0.0124</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.4582±0.0000</t>
+          <t>0.4938±0.0148</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -923,427 +923,427 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.5473±0.0668</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.6179±0.0393</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6179±0.0393</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6179±0.0393</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5462±0.0653</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5897±0.0076</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.6418±0.0342</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5912±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5912±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5912±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5681±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5901±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4901±0.0073</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5161±0.0130</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4560±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4681±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5744±0.0886</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5509±0.0712</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5509±0.0712</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5509±0.0712</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5282±0.0399</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6810±0.0155</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5495±0.0699</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5216±0.0306</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4842±0.0096</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4919±0.0205</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5905±0.0648</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6205±0.0081</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6205±0.0081</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6205±0.0081</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5465±0.0658</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6158±0.0531</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6282±0.0049</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.4842±0.0223</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6066±0.0225</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4780±0.0123</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.4945±0.0106</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5059±0.0061</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6590±0.0173</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6681±0.0314</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6681±0.0314</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6681±0.0314</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6652±0.0183</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6758±0.0103</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6993±0.0069</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.4912±0.0124</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4908±0.0058</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5033±0.0164</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5626±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6736±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5813±0.0550</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5813±0.0550</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5813±0.0550</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4462±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.5044±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.6018±0.0162</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4886±0.0095</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.4897±0.0105</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5828±0.0594</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5828±0.0594</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5828±0.0594</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.5502±0.0710</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5645±0.0069</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5700±0.0504</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>0.4718±0.0399</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5007±0.0005</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4989±0.0226</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5106±0.0361</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5220±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5714±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4549±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4846±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.5714±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6747±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6747±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6747±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.5758±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6253±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6780±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.4473±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4846±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4363±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5011±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4802±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4418±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4982±0.0019</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5077±0.0000</t>
+          <t>0.5245±0.0207</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5385±0.0000</t>
+          <t>0.5289±0.0019</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5385±0.0000</t>
+          <t>0.5289±0.0019</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5385±0.0000</t>
+          <t>0.5289±0.0019</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5077±0.0000</t>
+          <t>0.5095±0.0066</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5912±0.0000</t>
+          <t>0.6015±0.0374</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5352±0.0000</t>
+          <t>0.5333±0.0044</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6121±0.0000</t>
+          <t>0.6301±0.0141</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.6097±0.0000</t>
+          <t>0.6379±0.0171</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1385,427 +1385,427 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.6844±0.0251</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.7087±0.0177</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7087±0.0177</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.7087±0.0177</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6823±0.0222</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6637±0.0140</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7220±0.0119</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7014±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7014±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7014±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6419±0.0171</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6475±0.0028</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6494±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7023±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.6964±0.0358</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0283</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0283</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0283</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6775±0.0153</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7448±0.0044</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6871±0.0289</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3264±0.2723</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6124±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6271±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6325±0.0038</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6425±0.0174</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6801±0.0190</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0117</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0117</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6822±0.0117</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6760±0.0132</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7128±0.0225</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6901±0.0103</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.3634±0.2755</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7142±0.0128</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6310±0.0212</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6453±0.0051</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6690±0.0023</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7358±0.0032</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7424±0.0151</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7424±0.0151</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7424±0.0151</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7375±0.0043</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7425±0.0056</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7544±0.0064</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.4360±0.3084</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6555±0.0078</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6348±0.0151</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.6910±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7415±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0145</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0145</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6733±0.0145</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.5955±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6676±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6812±0.0106</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6502±0.0135</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6462±0.0038</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6824±0.0121</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6824±0.0121</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6824±0.0121</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6802±0.0191</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6869±0.0036</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6789±0.0132</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.4035±0.2897</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6670±0.0002</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6418±0.0056</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6615±0.0175</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6751±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6944±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6107±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6466±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6948±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7333±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7333±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7333±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.6951±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7132±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7363±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.5960±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6466±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.5799±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6672±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6446±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.5870±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6649±0.0019</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.6777±0.0097</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6828±0.0000</t>
+          <t>0.6795±0.0010</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6828±0.0000</t>
+          <t>0.6795±0.0010</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6828±0.0000</t>
+          <t>0.6795±0.0010</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.6708±0.0028</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7024±0.0000</t>
+          <t>0.7113±0.0166</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6812±0.0000</t>
+          <t>0.6818±0.0021</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5832±0.0000</t>
+          <t>0.5393±0.0695</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6628±0.0000</t>
+          <t>0.6781±0.0170</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5455±0.0000</t>
+          <t>0.6540±0.0388</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5623±0.0000</t>
+          <t>0.6687±0.0279</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6403±0.0000</t>
+          <t>0.6477±0.0133</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7036±0.0000</t>
+          <t>0.7390±0.0370</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.6945±0.0279</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7260±0.0000</t>
+          <t>0.7627±0.0148</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7260±0.0000</t>
+          <t>0.7627±0.0148</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7260±0.0000</t>
+          <t>0.7627±0.0148</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6480±0.0000</t>
+          <t>0.6932±0.0369</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6613±0.0000</t>
+          <t>0.6914±0.0044</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7423±0.0000</t>
+          <t>0.7576±0.0013</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5731±0.0000</t>
+          <t>0.6020±0.0135</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7393±0.0000</t>
+          <t>0.7191±0.0167</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6275±0.0000</t>
+          <t>0.6209±0.1040</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.5966±0.0000</t>
+          <t>0.7164±0.0084</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6291±0.0000</t>
+          <t>0.6407±0.0101</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5649±0.0000</t>
+          <t>0.6392±0.0158</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7161±0.0000</t>
+          <t>0.7673±0.0303</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7739±0.0042</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7739±0.0042</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7739±0.0042</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7693±0.0000</t>
+          <t>0.7708±0.0116</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7785±0.0000</t>
+          <t>0.7921±0.0077</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7925±0.0000</t>
+          <t>0.7852±0.0101</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5460±0.0000</t>
+          <t>0.5546±0.0192</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6381±0.0000</t>
+          <t>0.6293±0.0105</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.5519±0.0000</t>
+          <t>0.6487±0.0328</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5844±0.0000</t>
+          <t>0.6814±0.0415</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6377±0.0000</t>
+          <t>0.6438±0.0050</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6311±0.0000</t>
+          <t>0.6603±0.0105</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.6240±0.0000</t>
+          <t>0.6728±0.0368</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.6131±0.0000</t>
+          <t>0.6852±0.0186</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.6131±0.0000</t>
+          <t>0.6852±0.0186</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.6131±0.0000</t>
+          <t>0.6852±0.0186</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.6212±0.0000</t>
+          <t>0.6454±0.0593</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8479±0.0000</t>
+          <t>0.8231±0.0179</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5825±0.0000</t>
+          <t>0.6782±0.0226</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.4736±0.0000</t>
+          <t>0.5248±0.0790</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7027±0.0000</t>
+          <t>0.7375±0.0582</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4252±0.0000</t>
+          <t>0.6101±0.1177</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5631±0.0000</t>
+          <t>0.7001±0.0027</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6496±0.0000</t>
+          <t>0.6689±0.0227</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.7019±0.0315</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6980±0.0000</t>
+          <t>0.8015±0.0165</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7509±0.0000</t>
+          <t>0.7875±0.0283</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7509±0.0000</t>
+          <t>0.7875±0.0283</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7509±0.0000</t>
+          <t>0.7875±0.0283</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.6765±0.0000</t>
+          <t>0.7976±0.0096</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7737±0.0000</t>
+          <t>0.8093±0.0053</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7519±0.0000</t>
+          <t>0.7881±0.0138</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5861±0.0000</t>
+          <t>0.6471±0.0075</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6384±0.0000</t>
+          <t>0.6369±0.0039</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5524±0.0000</t>
+          <t>0.6130±0.0071</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5569±0.0000</t>
+          <t>0.6717±0.0034</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6371±0.0000</t>
+          <t>0.6423±0.0014</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6372±0.0000</t>
+          <t>0.6435±0.0014</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6333±0.0000</t>
+          <t>0.6307±0.0093</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6318±0.0000</t>
+          <t>0.6660±0.0425</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6318±0.0000</t>
+          <t>0.6660±0.0425</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6318±0.0000</t>
+          <t>0.6660±0.0425</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6323±0.0000</t>
+          <t>0.6286±0.0115</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.7326±0.0262</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6184±0.0000</t>
+          <t>0.6680±0.0148</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.5711±0.0000</t>
+          <t>0.5598±0.0850</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.6419±0.0066</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5484±0.0000</t>
+          <t>0.6153±0.0066</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5565±0.0000</t>
+          <t>0.6670±0.0344</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6378±0.0000</t>
+          <t>0.6423±0.0050</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6369±0.0000</t>
+          <t>0.6420±0.0055</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6522±0.0000</t>
+          <t>0.6466±0.0120</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6852±0.0235</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6852±0.0235</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6852±0.0235</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6886±0.0390</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6603±0.0000</t>
+          <t>0.8030±0.0057</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6567±0.0000</t>
+          <t>0.6640±0.0197</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5941±0.0000</t>
+          <t>0.5498±0.0804</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7503±0.0000</t>
+          <t>0.7387±0.0103</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4802±0.0000</t>
+          <t>0.6337±0.1136</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5008±0.0000</t>
+          <t>0.6581±0.1214</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6338±0.0000</t>
+          <t>0.6339±0.0037</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5875±0.0000</t>
+          <t>0.6113±0.0039</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7261±0.0000</t>
+          <t>0.7875±0.0139</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.6908±0.0000</t>
+          <t>0.7426±0.0181</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.6908±0.0000</t>
+          <t>0.7426±0.0181</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.6908±0.0000</t>
+          <t>0.7426±0.0181</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7618±0.0119</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7971±0.0000</t>
+          <t>0.8097±0.0037</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6871±0.0000</t>
+          <t>0.7312±0.0217</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6384±0.0000</t>
+          <t>0.6142±0.0511</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6886±0.0000</t>
+          <t>0.7190±0.0105</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.6287±0.0000</t>
+          <t>0.7239±0.0229</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6531±0.0000</t>
+          <t>0.7289±0.0202</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6418±0.0000</t>
+          <t>0.6747±0.0099</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7026±0.0000</t>
+          <t>0.7519±0.0312</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.7240±0.0115</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7316±0.0000</t>
+          <t>0.7647±0.0181</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7316±0.0000</t>
+          <t>0.7647±0.0181</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7316±0.0000</t>
+          <t>0.7647±0.0181</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6803±0.0000</t>
+          <t>0.7235±0.0207</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7115±0.0000</t>
+          <t>0.7374±0.0099</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7570±0.0000</t>
+          <t>0.7445±0.0259</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6320±0.0000</t>
+          <t>0.6521±0.0208</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7345±0.0000</t>
+          <t>0.7340±0.0138</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6595±0.0000</t>
+          <t>0.6544±0.1183</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.6154±0.0000</t>
+          <t>0.7620±0.0109</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6271±0.0000</t>
+          <t>0.6688±0.0039</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6175±0.0000</t>
+          <t>0.6727±0.0038</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7216±0.0000</t>
+          <t>0.7782±0.0239</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7682±0.0000</t>
+          <t>0.7715±0.0127</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7682±0.0000</t>
+          <t>0.7715±0.0127</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7682±0.0000</t>
+          <t>0.7715±0.0127</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7787±0.0000</t>
+          <t>0.7601±0.0244</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7636±0.0000</t>
+          <t>0.7700±0.0081</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7709±0.0000</t>
+          <t>0.7757±0.0049</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6046±0.0000</t>
+          <t>0.6185±0.0072</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6497±0.0000</t>
+          <t>0.6518±0.0227</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6492±0.0000</t>
+          <t>0.7169±0.0181</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6720±0.0000</t>
+          <t>0.7412±0.0238</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6387±0.0000</t>
+          <t>0.6689±0.0028</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6357±0.0000</t>
+          <t>0.6842±0.0133</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6496±0.0000</t>
+          <t>0.6736±0.0426</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6453±0.0000</t>
+          <t>0.6913±0.0287</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6453±0.0000</t>
+          <t>0.6913±0.0287</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6453±0.0000</t>
+          <t>0.6913±0.0287</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6488±0.0000</t>
+          <t>0.6701±0.0540</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8630±0.0000</t>
+          <t>0.8341±0.0127</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6340±0.0000</t>
+          <t>0.6791±0.0309</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5223±0.0000</t>
+          <t>0.6021±0.0646</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6904±0.0000</t>
+          <t>0.7193±0.0587</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4614±0.0000</t>
+          <t>0.6214±0.1252</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.6036±0.0000</t>
+          <t>0.7298±0.0092</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6420±0.0000</t>
+          <t>0.6949±0.0228</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6179±0.0000</t>
+          <t>0.7194±0.0314</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.7929±0.0072</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.7468±0.0425</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.7468±0.0425</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.7468±0.0425</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6671±0.0000</t>
+          <t>0.7897±0.0054</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7510±0.0000</t>
+          <t>0.7861±0.0019</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7306±0.0000</t>
+          <t>0.7579±0.0146</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6385±0.0000</t>
+          <t>0.6921±0.0119</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6442±0.0000</t>
+          <t>0.6544±0.0040</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6509±0.0000</t>
+          <t>0.7036±0.0078</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6507±0.0000</t>
+          <t>0.7334±0.0041</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6379±0.0000</t>
+          <t>0.6679±0.0086</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6378±0.0000</t>
+          <t>0.6686±0.0088</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6630±0.0131</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6420±0.0000</t>
+          <t>0.6877±0.0367</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6420±0.0000</t>
+          <t>0.6877±0.0367</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6420±0.0000</t>
+          <t>0.6877±0.0367</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6414±0.0000</t>
+          <t>0.6613±0.0147</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.6750±0.0000</t>
+          <t>0.7789±0.0188</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6400±0.0000</t>
+          <t>0.6626±0.0323</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6237±0.0000</t>
+          <t>0.6302±0.0594</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6294±0.0000</t>
+          <t>0.6462±0.0223</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6473±0.0000</t>
+          <t>0.7031±0.0051</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6532±0.0000</t>
+          <t>0.7297±0.0180</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6388±0.0000</t>
+          <t>0.6672±0.0043</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.6378±0.0000</t>
+          <t>0.6692±0.0038</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.6759±0.0030</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6618±0.0000</t>
+          <t>0.6892±0.0243</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6618±0.0000</t>
+          <t>0.6892±0.0243</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6618±0.0000</t>
+          <t>0.6892±0.0243</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6614±0.0000</t>
+          <t>0.7074±0.0315</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7425±0.0000</t>
+          <t>0.8366±0.0034</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6715±0.0000</t>
+          <t>0.6686±0.0318</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6517±0.0000</t>
+          <t>0.6110±0.0697</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7414±0.0000</t>
+          <t>0.7334±0.0135</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4903±0.0000</t>
+          <t>0.6563±0.1201</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5108±0.0000</t>
+          <t>0.6625±0.1234</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6365±0.0000</t>
+          <t>0.6616±0.0045</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.5995±0.0000</t>
+          <t>0.6417±0.0080</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7158±0.0000</t>
+          <t>0.7635±0.0092</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6884±0.0202</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6884±0.0202</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6415±0.0000</t>
+          <t>0.6884±0.0202</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7402±0.0000</t>
+          <t>0.7445±0.0080</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7742±0.0000</t>
+          <t>0.7920±0.0117</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6344±0.0000</t>
+          <t>0.6746±0.0249</t>
         </is>
       </c>
     </row>
